--- a/OUTPUT/reverse_Q4UZF6_Xanthomonas_campestris_pv__campestris_str__8004.xlsx
+++ b/OUTPUT/reverse_Q4UZF6_Xanthomonas_campestris_pv__campestris_str__8004.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>GGTGCG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>CGCACC</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>GCGTGG</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.0122</v>
+        <v>0.01239504198320672</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +506,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>CGGTG</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>CACCG</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GTGGC</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.0824</v>
+        <v>0.08256697321071571</v>
       </c>
     </row>
     <row r="4">
@@ -535,16 +535,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="5">
@@ -569,11 +569,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="6">
@@ -598,11 +598,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="7">
@@ -622,16 +622,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="8">
@@ -656,11 +656,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CG</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
     <row r="9">
@@ -680,16 +680,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>GG</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>GG</t>
-        </is>
-      </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.9998000799680128</v>
       </c>
     </row>
   </sheetData>
